--- a/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>KELY.B</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1191100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1038100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1057500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1045100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1232200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1118000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1217200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1268300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1233800</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>949600</v>
+      </c>
+      <c r="E9" s="3">
         <v>816400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>843800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>839400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>994000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>889500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>976600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1014200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>983600</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E10" s="3">
         <v>221700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>213700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>205700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>238200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>228500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>240600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>254100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>250200</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -808,8 +820,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -866,66 +882,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E15" s="3">
         <v>14500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10200</v>
       </c>
-      <c r="G15" s="3">
-        <v>100</v>
-      </c>
       <c r="H15" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="I15" s="3">
         <v>10000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -934,66 +959,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1167300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1035600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1031000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1027600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1213900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1102500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1203000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1251000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1219800</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,153 +1037,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E21" s="3">
         <v>15800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28400</v>
       </c>
-      <c r="G21" s="3">
-        <v>14900</v>
-      </c>
       <c r="H21" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I21" s="3">
         <v>26000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>23100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E22" s="3">
         <v>4500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1179,66 +1227,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>25800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1266,8 +1323,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,8 +1355,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1324,8 +1387,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1353,66 +1419,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1440,71 +1515,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1516,8 +1600,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1529,37 +1614,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E41" s="3">
         <v>32800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>125800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>117200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>124800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>111700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1587,37 +1676,43 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1271900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1249700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1193900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1153100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1160600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1388200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1423600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1438500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1491600</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1645,71 +1740,80 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="G45" s="3">
-        <v>294700</v>
-      </c>
       <c r="H45" s="3">
+        <v>294800</v>
+      </c>
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1365500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1357500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1310800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1436800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1626600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1591500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1628200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1632500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1715200</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>11000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -1720,66 +1824,72 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>6400</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3">
         <v>6400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>6400</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E48" s="3">
         <v>81700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>79900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>71800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>71700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>88700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>90400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>93600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E49" s="3">
         <v>638300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>644900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>283600</v>
       </c>
-      <c r="G49" s="3">
-        <v>151100</v>
-      </c>
       <c r="H49" s="3">
-        <v>151100</v>
+        <v>288800</v>
       </c>
       <c r="I49" s="3">
         <v>151100</v>
@@ -1788,10 +1898,13 @@
         <v>151100</v>
       </c>
       <c r="K49" s="3">
+        <v>151100</v>
+      </c>
+      <c r="L49" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1819,8 +1932,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1848,37 +1964,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E52" s="3">
         <v>303000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>290300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>284300</v>
       </c>
-      <c r="G52" s="3">
-        <v>411100</v>
-      </c>
       <c r="H52" s="3">
+        <v>273400</v>
+      </c>
+      <c r="I52" s="3">
         <v>397000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>410500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>409500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>230800</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,37 +2028,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2632300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2688900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2628200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2395400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2581600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2550000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2595000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2588600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2663800</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1948,8 +2076,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1961,37 +2090,41 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>607400</v>
+      </c>
+      <c r="E57" s="3">
         <v>598600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>590600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>576700</v>
       </c>
-      <c r="G57" s="3">
-        <v>641200</v>
-      </c>
       <c r="H57" s="3">
+        <v>644800</v>
+      </c>
+      <c r="I57" s="3">
         <v>642200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>692600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>679700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>717600</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -1999,144 +2132,159 @@
         <v>12700</v>
       </c>
       <c r="E58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F58" s="3">
         <v>12400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="H58" s="3">
         <v>8400</v>
       </c>
-      <c r="G58" s="3">
-        <v>8400</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E59" s="3">
         <v>27100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22300</v>
       </c>
-      <c r="F59" s="3">
-        <v>24500</v>
-      </c>
       <c r="G59" s="3">
-        <v>192000</v>
+        <v>20100</v>
       </c>
       <c r="H59" s="3">
+        <v>188400</v>
+      </c>
+      <c r="I59" s="3">
         <v>59300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>54500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>57900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>826500</v>
+      </c>
+      <c r="E60" s="3">
         <v>841000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>812300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>797500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1019900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1025300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1054900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1050900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1128800</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>290300</v>
+      </c>
+      <c r="E61" s="3">
         <v>280200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>260000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>42000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E62" s="3">
         <v>42500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>49600</v>
       </c>
-      <c r="G62" s="3">
-        <v>47300</v>
-      </c>
       <c r="H62" s="3">
+        <v>47700</v>
+      </c>
+      <c r="I62" s="3">
         <v>51900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>52600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>51900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,8 +2312,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2193,8 +2344,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2222,37 +2376,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1397700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1407000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1348300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1118600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1327900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1314300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1353100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1340800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1409600</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2264,8 +2424,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2293,8 +2454,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2322,8 +2486,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +2518,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2380,37 +2550,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1230200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1264700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1266700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1264800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1241700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1233000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1229100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1224400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1216300</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2438,8 +2614,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,8 +2646,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,37 +2678,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1234600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1281900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1279900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1276800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1253700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1235700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1241900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1247800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1254200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2554,71 +2742,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2630,37 +2827,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E83" s="3">
         <v>12400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>13000</v>
       </c>
       <c r="H83" s="3">
         <v>13000</v>
       </c>
       <c r="I83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J83" s="3">
         <v>13400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12500</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2688,8 +2889,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2717,8 +2921,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2746,8 +2953,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2775,8 +2985,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2804,37 +3017,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-25500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>43300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>36900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2846,37 +3065,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2904,8 +3127,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2933,37 +3159,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-425200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>72100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2975,16 +3207,17 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E96" s="3">
         <v>2800</v>
-      </c>
-      <c r="E96" s="3">
-        <v>2700</v>
       </c>
       <c r="F96" s="3">
         <v>2700</v>
@@ -2996,16 +3229,19 @@
         <v>2700</v>
       </c>
       <c r="I96" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="J96" s="3">
         <v>2800</v>
       </c>
       <c r="K96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L96" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3033,8 +3269,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3062,8 +3301,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3091,91 +3333,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E100" s="3">
         <v>15700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>206300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13200</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-163300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>41300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>41100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>31700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>KELY.B</t>
   </si>
@@ -656,159 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45018</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1164900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1191100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1038100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1057500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1045100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1232200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1118000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1217200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1268300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1233800</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>928400</v>
+      </c>
+      <c r="E9" s="3">
         <v>949600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>816400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>843800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>839400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>994000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>889500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>976600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1014200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>983600</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>236500</v>
+      </c>
+      <c r="E10" s="3">
         <v>241500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>221700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>213700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>205700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>238200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>228500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>240600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>254100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>250200</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +834,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -853,8 +867,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,72 +902,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E14" s="3">
         <v>81900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-9300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E15" s="3">
         <v>-9900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-8800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,72 +986,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1143400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1167300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1035600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1031000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1027600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1213900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1102500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1203000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1251000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1219800</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E18" s="3">
         <v>23800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,168 +1071,184 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E21" s="3">
         <v>19800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>28400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-23800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,72 +1279,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>25800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-31000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>25200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,8 +1419,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,72 +1489,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-31800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>25800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,77 +1594,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-31800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>25800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45018</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,40 +1701,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E41" s="3">
         <v>39000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>125800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>117200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>124800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1679,40 +1769,46 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1267900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1271900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1249700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1193900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1153100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1160600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1388200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1423600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1438500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1491600</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1743,80 +1839,89 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>294800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1351000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1365500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1357500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1310800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1436800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1626600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1591500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1628200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1632500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1715200</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>400</v>
+      </c>
+      <c r="E47" s="3">
         <v>11000</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -1827,72 +1932,78 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
-        <v>6400</v>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>6400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
+      <c r="K47" s="3">
+        <v>6400</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E48" s="3">
         <v>72800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>81700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>79900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>71800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>71700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>88700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>90400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>93600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>552500</v>
+      </c>
+      <c r="E49" s="3">
         <v>578400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>638300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>644900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>283600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>288800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>151100</v>
       </c>
       <c r="J49" s="3">
         <v>151100</v>
@@ -1901,10 +2012,13 @@
         <v>151100</v>
       </c>
       <c r="L49" s="3">
+        <v>151100</v>
+      </c>
+      <c r="M49" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,40 +2084,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>290300</v>
+      </c>
+      <c r="E52" s="3">
         <v>274500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>303000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>290300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>284300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>273400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>397000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>410500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>409500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>230800</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,40 +2154,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2594900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2632300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2688900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2628200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2395400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2581600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2550000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2595000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2588600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2663800</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,200 +2221,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>593600</v>
+      </c>
+      <c r="E57" s="3">
         <v>607400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>598600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>590600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>576700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>644800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>642200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>692600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>679700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>717600</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12700</v>
+        <v>12500</v>
       </c>
       <c r="E58" s="3">
         <v>12700</v>
       </c>
       <c r="F58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="G58" s="3">
         <v>12400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E59" s="3">
         <v>23500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>188400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>59300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>54500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>57900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>822900</v>
+      </c>
+      <c r="E60" s="3">
         <v>826500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>841000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>812300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>797500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1019900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1025300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1054900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1050900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1128800</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E61" s="3">
         <v>290300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>280200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>260000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>52600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E62" s="3">
         <v>40600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>43400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>49600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>51900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>52600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>51900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,40 +2534,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1354400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1397700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1407000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1348300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1118600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1327900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1314300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1353100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1340800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1409600</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2521,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,40 +2724,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1233200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1230200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1264700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1266700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1264800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1241700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1233000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1229100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1224400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1216300</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,40 +2864,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1240500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1234600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1281900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1279900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1276800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1253700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1235700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1241900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1247800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1254200</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,77 +2934,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45018</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-31800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>25800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,40 +3026,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E83" s="3">
         <v>12100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>13000</v>
       </c>
       <c r="I83" s="3">
         <v>13000</v>
       </c>
       <c r="J83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K83" s="3">
         <v>13400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12500</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,40 +3234,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E89" s="3">
         <v>15000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-20300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-25500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>43300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>36900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,40 +3286,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,40 +3389,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-425200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>72100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,19 +3441,20 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E96" s="3">
         <v>2700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>2700</v>
       </c>
       <c r="G96" s="3">
         <v>2700</v>
@@ -3232,16 +3466,19 @@
         <v>2700</v>
       </c>
       <c r="J96" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="K96" s="3">
         <v>2800</v>
       </c>
       <c r="L96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M96" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,100 +3579,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>206300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13200</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>4100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E102" s="3">
         <v>5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-163300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>41300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>41100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>31700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>KELY.B</t>
   </si>
@@ -656,172 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45018</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1101800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1164900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1191100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1038100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1057500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1045100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1232200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1118000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1217200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1268300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1233800</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>876300</v>
+      </c>
+      <c r="E9" s="3">
         <v>928400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>949600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>816400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>843800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>839400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>994000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>889500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>976600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1014200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>983600</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>225500</v>
+      </c>
+      <c r="E10" s="3">
         <v>236500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>241500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>221700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>213700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>205700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>238200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>228500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>240600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>254100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>250200</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +848,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -870,8 +884,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,78 +922,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>10700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>81900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>22100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-9300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>15400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E15" s="3">
         <v>12800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-9900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-8800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,78 +1013,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1077600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1143400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1167300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1035600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1031000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1027600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1213900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1102500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1203000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1251000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1219800</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E18" s="3">
         <v>21500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>26500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,183 +1105,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E21" s="3">
         <v>34300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>28400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="3">
         <v>4000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E23" s="3">
         <v>7600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-23800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1331,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>25800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1483,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,78 +1559,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1673,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45018</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,43 +1788,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E41" s="3">
         <v>28200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>125800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>117200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>124800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>111700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,43 +1862,49 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1181100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1267900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1271900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1249700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1193900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1153100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1160600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1388200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1423600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1438500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1491600</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1842,78 +1938,87 @@
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
       <c r="H45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I45" s="3">
         <v>2300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>294800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1253100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1351000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1365500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1357500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1310800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1436800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1626600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1591500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1628200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1632500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1715200</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1921,10 +2026,10 @@
         <v>400</v>
       </c>
       <c r="E47" s="3">
+        <v>400</v>
+      </c>
+      <c r="F47" s="3">
         <v>11000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -1935,78 +2040,84 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>6400</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>6400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
+      <c r="L47" s="3">
+        <v>6400</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E48" s="3">
         <v>69600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>72800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>81700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>79900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>71800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>71700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>88700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>90400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>93600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>545100</v>
+      </c>
+      <c r="E49" s="3">
         <v>552500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>578400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>638300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>644900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>283600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>288800</v>
-      </c>
-      <c r="J49" s="3">
-        <v>151100</v>
       </c>
       <c r="K49" s="3">
         <v>151100</v>
@@ -2015,10 +2126,13 @@
         <v>151100</v>
       </c>
       <c r="M49" s="3">
+        <v>151100</v>
+      </c>
+      <c r="N49" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,43 +2204,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>308700</v>
+      </c>
+      <c r="E52" s="3">
         <v>290300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>274500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>303000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>290300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>284300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>273400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>397000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>410500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>409500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>230800</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,43 +2280,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2511900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2594900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2632300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2688900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2628200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2395400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2581600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2550000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2595000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2588600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2663800</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,218 +2352,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>593600</v>
+        <v>611900</v>
       </c>
       <c r="E57" s="3">
+        <v>595300</v>
+      </c>
+      <c r="F57" s="3">
         <v>607400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>598600</v>
       </c>
-      <c r="G57" s="3">
-        <v>590600</v>
-      </c>
       <c r="H57" s="3">
+        <v>587200</v>
+      </c>
+      <c r="I57" s="3">
         <v>576700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>644800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>642200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>692600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>679700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>717600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E58" s="3">
         <v>12500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>12700</v>
       </c>
       <c r="F58" s="3">
         <v>12700</v>
       </c>
       <c r="G58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="H58" s="3">
         <v>12400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>23500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>27100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I59" s="3">
         <v>20100</v>
       </c>
-      <c r="E59" s="3">
-        <v>23500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>27100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>22300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>20100</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>188400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>59300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>57900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>826700</v>
+      </c>
+      <c r="E60" s="3">
         <v>822900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>826500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>841000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>812300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>797500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1019900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1025300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1054900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1050900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1128800</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E61" s="3">
         <v>253900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>290300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>280200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>260000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>53400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E62" s="3">
         <v>41200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>40600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>43400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>49600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>51900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>52600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,43 +2692,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1245800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1354400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1397700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1407000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1348300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1118600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1327900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1314300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1353100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1340800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1409600</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,43 +2898,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1249500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1233200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1230200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1264700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1266700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1264800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1241700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1233000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1229100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1224400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1216300</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,43 +3050,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1266100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1240500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1234600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1281900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1279900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1276800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1253700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1235700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1241900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1247800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1254200</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3126,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45018</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,43 +3225,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E83" s="3">
         <v>10200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>13000</v>
       </c>
       <c r="J83" s="3">
         <v>13000</v>
       </c>
       <c r="K83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="L83" s="3">
         <v>13400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12500</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3451,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E89" s="3">
         <v>23900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>43300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>36900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,43 +3507,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,43 +3619,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E94" s="3">
         <v>3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-425200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>72100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,22 +3675,23 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E96" s="3">
         <v>2800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2800</v>
-      </c>
-      <c r="G96" s="3">
-        <v>2700</v>
       </c>
       <c r="H96" s="3">
         <v>2700</v>
@@ -3469,16 +3703,19 @@
         <v>2700</v>
       </c>
       <c r="K96" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="L96" s="3">
         <v>2800</v>
       </c>
       <c r="M96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N96" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,109 +3825,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-133200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-39500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>206300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13200</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-163300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>41300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>41100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>31700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KELY.B_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>KELY.B</t>
   </si>
@@ -656,198 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1049200</v>
+      </c>
+      <c r="E8" s="3">
         <v>935000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1101800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1164900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1191100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1038100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1057500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1045100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1232200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1118000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1217200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1268300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1233800</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>852200</v>
+      </c>
+      <c r="E9" s="3">
         <v>741000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>876300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>928400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>949600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>816400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>843800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>839400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>994000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>889500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>976600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1014200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>983600</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E10" s="3">
         <v>194000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>225500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>236500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>241500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>221700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>213700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>205700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>238200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>228500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>240600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>254100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>250200</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +917,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,90 +961,99 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E14" s="3">
         <v>105200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>74100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-9300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E15" s="3">
         <v>12600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-9900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-8800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,90 +1066,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1043200</v>
+      </c>
+      <c r="E17" s="3">
         <v>931900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1077600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1143400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1167300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1029100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1031000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1027600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1213900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1102500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1203000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1251000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1219800</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,213 +1172,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E21" s="3">
         <v>15500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>34300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>23100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-103700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E24" s="3">
         <v>46400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-23800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1434,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-128800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-150100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>25800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-128800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-150100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1566,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,90 +1698,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-128800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-150100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1830,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-128800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-150100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,49 +1961,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E41" s="3">
         <v>30100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>125800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>117200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>124800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>153700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1958,49 +2047,55 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1188700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1195600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1181100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1267900</v>
       </c>
-      <c r="G43" s="3">
-        <v>1271900</v>
-      </c>
       <c r="H43" s="3">
+        <v>1255500</v>
+      </c>
+      <c r="I43" s="3">
         <v>1248600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1193900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1153100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1160600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1388200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1423600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1438500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1491600</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2040,95 +2135,104 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>294800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1268300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1279800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1253100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1351000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1365500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1357500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1310800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1436800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1626600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1591500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1628200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1632500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1715200</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>400</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
         <v>400</v>
@@ -2137,7 +2241,7 @@
         <v>400</v>
       </c>
       <c r="G47" s="3">
-        <v>11000</v>
+        <v>400</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -2151,90 +2255,96 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>6400</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>6400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
+      <c r="N47" s="3">
+        <v>6400</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E48" s="3">
         <v>66400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>67300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>81700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>79900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>71800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>71700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>88700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>90400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>93600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>428300</v>
+      </c>
+      <c r="E49" s="3">
         <v>435700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>545100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>552500</v>
       </c>
-      <c r="G49" s="3">
-        <v>578400</v>
-      </c>
       <c r="H49" s="3">
+        <v>560500</v>
+      </c>
+      <c r="I49" s="3">
         <v>638300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>644900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>283600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>288800</v>
-      </c>
-      <c r="L49" s="3">
-        <v>151100</v>
       </c>
       <c r="M49" s="3">
         <v>151100</v>
@@ -2243,10 +2353,13 @@
         <v>151100</v>
       </c>
       <c r="O49" s="3">
+        <v>151100</v>
+      </c>
+      <c r="P49" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,49 +2443,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>327400</v>
+      </c>
+      <c r="E52" s="3">
         <v>321700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>308700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>290300</v>
       </c>
-      <c r="G52" s="3">
-        <v>274500</v>
-      </c>
       <c r="H52" s="3">
+        <v>303400</v>
+      </c>
+      <c r="I52" s="3">
         <v>303000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>290300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>284300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>273400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>397000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>410500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>409500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>230800</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2531,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2250600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2393100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2511900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2594900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2632300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2688900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2628200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2395400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2581600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2550000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2595000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2588600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2663800</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,254 +2613,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>626700</v>
+      </c>
+      <c r="E57" s="3">
         <v>601900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>611900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>595300</v>
       </c>
-      <c r="G57" s="3">
-        <v>607400</v>
-      </c>
       <c r="H57" s="3">
+        <v>608300</v>
+      </c>
+      <c r="I57" s="3">
         <v>600000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>587200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>576700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>644800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>642200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>692600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>679700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>717600</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E58" s="3">
         <v>12400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>12700</v>
       </c>
       <c r="H58" s="3">
         <v>12700</v>
       </c>
       <c r="I58" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J58" s="3">
         <v>12400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>8400</v>
       </c>
       <c r="K58" s="3">
         <v>8400</v>
       </c>
       <c r="L58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="M58" s="3">
         <v>13200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18400</v>
       </c>
-      <c r="G59" s="3">
-        <v>23500</v>
-      </c>
       <c r="H59" s="3">
-        <v>25700</v>
+        <v>22600</v>
       </c>
       <c r="I59" s="3">
         <v>25700</v>
       </c>
       <c r="J59" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K59" s="3">
         <v>24500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>188400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>59300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>54500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>57900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>821800</v>
+      </c>
+      <c r="E60" s="3">
         <v>806500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>826700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>822900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>826500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>841000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>812300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>797500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1019900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1025300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1054900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1050900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1128800</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>146800</v>
+      </c>
+      <c r="E61" s="3">
         <v>165100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>121800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>253900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>290300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>280200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>260000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>42000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E62" s="3">
         <v>41500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>41200</v>
       </c>
-      <c r="G62" s="3">
-        <v>40600</v>
-      </c>
       <c r="H62" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I62" s="3">
         <v>42500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>43400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>49600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3007,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1274100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1278000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1245800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1354400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1397700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1407000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1348300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1118600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1327900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1314300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1353100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1340800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1409600</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3245,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>965100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1096600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1249500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1233200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1230200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1264700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1266700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1264800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1241700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1233000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1229100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1224400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1216300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3421,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>976500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1115100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1266100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1240500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1234600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1281900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1279900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1276800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1253700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1235700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1241900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1247800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1254200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3509,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-128800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-150100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,49 +3622,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E83" s="3">
         <v>14200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>13000</v>
       </c>
       <c r="L83" s="3">
         <v>13000</v>
       </c>
       <c r="M83" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N83" s="3">
         <v>13400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12500</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +3884,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>95400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>57700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>43300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>36900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,49 +3948,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4078,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>21500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-425200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>72100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,28 +4142,29 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E96" s="3">
         <v>2800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2800</v>
-      </c>
-      <c r="I96" s="3">
-        <v>2700</v>
       </c>
       <c r="J96" s="3">
         <v>2700</v>
@@ -3943,16 +4176,19 @@
         <v>2700</v>
       </c>
       <c r="M96" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="N96" s="3">
         <v>2800</v>
       </c>
       <c r="O96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P96" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,127 +4316,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E100" s="3">
         <v>41300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-133200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-39500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>206300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-24800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13200</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>9700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>10900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-163300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>41300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>41100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31700</v>
       </c>
     </row>
